--- a/R_analysis/output/tables/Tabela_Desigualdade_Temporal.xlsx
+++ b/R_analysis/output/tables/Tabela_Desigualdade_Temporal.xlsx
@@ -387,7 +387,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C2">
@@ -406,7 +406,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C3">
@@ -425,7 +425,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C4">
@@ -444,7 +444,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C5">
@@ -463,7 +463,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C6">
@@ -482,7 +482,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C7">
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C8">
@@ -520,7 +520,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C9">
@@ -539,7 +539,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="C10">
@@ -558,7 +558,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="C11">
